--- a/#zonauang_anonymized.xlsx
+++ b/#zonauang_anonymized.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关注的userName</t>
+          <t>followed_userName</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>粉丝的userName</t>
+          <t>follower_userName</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发文量</t>
+          <t>Number of Publications</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">

--- a/#zonauang_anonymized.xlsx
+++ b/#zonauang_anonymized.xlsx
@@ -523,7 +523,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -570,7 +570,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -615,7 +615,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -704,7 +704,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -747,7 +747,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -829,7 +829,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -1868,7 +1868,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K212" t="inlineStr"/>
@@ -8087,7 +8087,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K213" t="inlineStr"/>
@@ -8128,7 +8128,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K214" t="inlineStr"/>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K215" t="inlineStr"/>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K216" t="inlineStr"/>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K217" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K218" t="inlineStr"/>
@@ -11889,7 +11889,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K320" t="inlineStr"/>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K321" t="inlineStr"/>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K322" t="inlineStr"/>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K323" t="inlineStr"/>
@@ -12071,7 +12071,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K324" t="inlineStr"/>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K325" t="inlineStr"/>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K326" t="inlineStr"/>
@@ -17493,7 +17493,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K480" t="inlineStr"/>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K481" t="inlineStr"/>
@@ -17571,7 +17571,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K482" t="inlineStr"/>
@@ -17610,7 +17610,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K483" t="inlineStr"/>
@@ -17649,7 +17649,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K484" t="inlineStr"/>
@@ -17688,7 +17688,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K485" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="K486" t="inlineStr"/>
